--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119932296</v>
+        <v>119932421</v>
       </c>
       <c r="B2" t="n">
-        <v>97885</v>
+        <v>110037</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691346</v>
+        <v>691326</v>
       </c>
       <c r="R2" t="n">
-        <v>6684612</v>
+        <v>6684670</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931537</v>
+        <v>119931411</v>
       </c>
       <c r="B4" t="n">
         <v>97929</v>
@@ -948,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R4" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119932421</v>
+        <v>119931614</v>
       </c>
       <c r="B5" t="n">
-        <v>110037</v>
+        <v>101074</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691326</v>
+        <v>691229</v>
       </c>
       <c r="R5" t="n">
-        <v>6684670</v>
+        <v>6684627</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119931614</v>
+        <v>119932296</v>
       </c>
       <c r="B6" t="n">
-        <v>101074</v>
+        <v>97885</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,37 +1139,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691229</v>
+        <v>691346</v>
       </c>
       <c r="R6" t="n">
-        <v>6684627</v>
+        <v>6684612</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119932536</v>
+        <v>119931537</v>
       </c>
       <c r="B8" t="n">
-        <v>110037</v>
+        <v>97929</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,43 +1372,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691318</v>
+        <v>691229</v>
       </c>
       <c r="R8" t="n">
-        <v>6684689</v>
+        <v>6684627</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119931411</v>
+        <v>119932536</v>
       </c>
       <c r="B9" t="n">
-        <v>97929</v>
+        <v>110037</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,34 +1484,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691258</v>
+        <v>691318</v>
       </c>
       <c r="R9" t="n">
-        <v>6684672</v>
+        <v>6684689</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119931454</v>
+        <v>119931537</v>
       </c>
       <c r="B3" t="n">
-        <v>97885</v>
+        <v>97929</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R3" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931411</v>
+        <v>119931614</v>
       </c>
       <c r="B4" t="n">
-        <v>97929</v>
+        <v>101074</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R4" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119931614</v>
+        <v>119931411</v>
       </c>
       <c r="B5" t="n">
-        <v>101074</v>
+        <v>97929</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R5" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119932296</v>
+        <v>119932536</v>
       </c>
       <c r="B6" t="n">
-        <v>97885</v>
+        <v>110037</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,26 +1139,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1172,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691346</v>
+        <v>691318</v>
       </c>
       <c r="R6" t="n">
-        <v>6684612</v>
+        <v>6684689</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1356,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119931537</v>
+        <v>119931454</v>
       </c>
       <c r="B8" t="n">
-        <v>97929</v>
+        <v>97885</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1372,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R8" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119932536</v>
+        <v>119932296</v>
       </c>
       <c r="B9" t="n">
-        <v>110037</v>
+        <v>97885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,26 +1484,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1517,13 +1517,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691318</v>
+        <v>691346</v>
       </c>
       <c r="R9" t="n">
-        <v>6684689</v>
+        <v>6684612</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119932421</v>
+        <v>119931411</v>
       </c>
       <c r="B2" t="n">
-        <v>110037</v>
+        <v>97929</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691326</v>
+        <v>691258</v>
       </c>
       <c r="R2" t="n">
-        <v>6684670</v>
+        <v>6684672</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119931537</v>
+        <v>119932421</v>
       </c>
       <c r="B3" t="n">
-        <v>97929</v>
+        <v>110037</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691229</v>
+        <v>691326</v>
       </c>
       <c r="R3" t="n">
-        <v>6684627</v>
+        <v>6684670</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931614</v>
+        <v>119931706</v>
       </c>
       <c r="B4" t="n">
-        <v>101074</v>
+        <v>110037</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691229</v>
+        <v>691300</v>
       </c>
       <c r="R4" t="n">
-        <v>6684627</v>
+        <v>6684669</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119931411</v>
+        <v>119932296</v>
       </c>
       <c r="B5" t="n">
-        <v>97929</v>
+        <v>97885</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1027,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691258</v>
+        <v>691346</v>
       </c>
       <c r="R5" t="n">
-        <v>6684672</v>
+        <v>6684612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119932536</v>
+        <v>119931537</v>
       </c>
       <c r="B6" t="n">
-        <v>110037</v>
+        <v>97929</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,43 +1148,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691318</v>
+        <v>691229</v>
       </c>
       <c r="R6" t="n">
-        <v>6684689</v>
+        <v>6684627</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119931706</v>
+        <v>119932536</v>
       </c>
       <c r="B7" t="n">
         <v>110037</v>
@@ -1277,17 +1277,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691300</v>
+        <v>691318</v>
       </c>
       <c r="R7" t="n">
-        <v>6684669</v>
+        <v>6684689</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119931454</v>
+        <v>119931614</v>
       </c>
       <c r="B8" t="n">
-        <v>97885</v>
+        <v>101074</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1396,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R8" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1431,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119932296</v>
+        <v>119931454</v>
       </c>
       <c r="B9" t="n">
         <v>97885</v>
@@ -1501,29 +1510,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691346</v>
+        <v>691258</v>
       </c>
       <c r="R9" t="n">
-        <v>6684612</v>
+        <v>6684672</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119931411</v>
+        <v>119931706</v>
       </c>
       <c r="B2" t="n">
-        <v>97929</v>
+        <v>110061</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691258</v>
+        <v>691300</v>
       </c>
       <c r="R2" t="n">
-        <v>6684672</v>
+        <v>6684669</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119932421</v>
+        <v>119931614</v>
       </c>
       <c r="B3" t="n">
-        <v>110037</v>
+        <v>101097</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691326</v>
+        <v>691229</v>
       </c>
       <c r="R3" t="n">
-        <v>6684670</v>
+        <v>6684627</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931706</v>
+        <v>119932296</v>
       </c>
       <c r="B4" t="n">
-        <v>110037</v>
+        <v>97908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691300</v>
+        <v>691346</v>
       </c>
       <c r="R4" t="n">
-        <v>6684669</v>
+        <v>6684612</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119932296</v>
+        <v>119931454</v>
       </c>
       <c r="B5" t="n">
-        <v>97885</v>
+        <v>97908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1044,29 +1053,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691346</v>
+        <v>691258</v>
       </c>
       <c r="R5" t="n">
-        <v>6684612</v>
+        <v>6684672</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119931537</v>
+        <v>119932421</v>
       </c>
       <c r="B6" t="n">
-        <v>97929</v>
+        <v>110061</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691229</v>
+        <v>691326</v>
       </c>
       <c r="R6" t="n">
-        <v>6684627</v>
+        <v>6684670</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,7 +1247,7 @@
         <v>119932536</v>
       </c>
       <c r="B7" t="n">
-        <v>110037</v>
+        <v>110061</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119931614</v>
+        <v>119931411</v>
       </c>
       <c r="B8" t="n">
-        <v>101074</v>
+        <v>97952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R8" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119931454</v>
+        <v>119931537</v>
       </c>
       <c r="B9" t="n">
-        <v>97885</v>
+        <v>97952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R9" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119931706</v>
+        <v>119932421</v>
       </c>
       <c r="B2" t="n">
         <v>110061</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691300</v>
+        <v>691326</v>
       </c>
       <c r="R2" t="n">
-        <v>6684669</v>
+        <v>6684670</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119932296</v>
+        <v>119931537</v>
       </c>
       <c r="B4" t="n">
-        <v>97908</v>
+        <v>97952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691346</v>
+        <v>691229</v>
       </c>
       <c r="R4" t="n">
-        <v>6684612</v>
+        <v>6684627</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119931454</v>
+        <v>119932296</v>
       </c>
       <c r="B5" t="n">
         <v>97908</v>
@@ -1053,20 +1044,29 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691258</v>
+        <v>691346</v>
       </c>
       <c r="R5" t="n">
-        <v>6684672</v>
+        <v>6684612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119932421</v>
+        <v>119931454</v>
       </c>
       <c r="B6" t="n">
-        <v>110061</v>
+        <v>97908</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691326</v>
+        <v>691258</v>
       </c>
       <c r="R6" t="n">
-        <v>6684670</v>
+        <v>6684672</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,7 +1244,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119932536</v>
+        <v>119931706</v>
       </c>
       <c r="B7" t="n">
         <v>110061</v>
@@ -1277,26 +1277,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691318</v>
+        <v>691300</v>
       </c>
       <c r="R7" t="n">
-        <v>6684689</v>
+        <v>6684669</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119931411</v>
+        <v>119932536</v>
       </c>
       <c r="B8" t="n">
-        <v>97952</v>
+        <v>110061</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,34 +1372,43 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691258</v>
+        <v>691318</v>
       </c>
       <c r="R8" t="n">
-        <v>6684672</v>
+        <v>6684689</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,7 +1477,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119931537</v>
+        <v>119931411</v>
       </c>
       <c r="B9" t="n">
         <v>97952</v>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R9" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119932421</v>
+        <v>119932536</v>
       </c>
       <c r="B2" t="n">
         <v>110061</v>
@@ -708,17 +708,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691326</v>
+        <v>691318</v>
       </c>
       <c r="R2" t="n">
-        <v>6684670</v>
+        <v>6684689</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119931614</v>
+        <v>119932296</v>
       </c>
       <c r="B3" t="n">
-        <v>101097</v>
+        <v>97908</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +812,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691229</v>
+        <v>691346</v>
       </c>
       <c r="R3" t="n">
-        <v>6684627</v>
+        <v>6684612</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931537</v>
+        <v>119931454</v>
       </c>
       <c r="B4" t="n">
-        <v>97952</v>
+        <v>97908</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R4" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +992,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +1002,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119932296</v>
+        <v>119931706</v>
       </c>
       <c r="B5" t="n">
-        <v>97908</v>
+        <v>110061</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,46 +1045,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691346</v>
+        <v>691300</v>
       </c>
       <c r="R5" t="n">
-        <v>6684612</v>
+        <v>6684669</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119931454</v>
+        <v>119931537</v>
       </c>
       <c r="B6" t="n">
-        <v>97908</v>
+        <v>97952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1157,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R6" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119931706</v>
+        <v>119931411</v>
       </c>
       <c r="B7" t="n">
-        <v>110061</v>
+        <v>97952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691300</v>
+        <v>691258</v>
       </c>
       <c r="R7" t="n">
-        <v>6684669</v>
+        <v>6684672</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119932536</v>
+        <v>119932421</v>
       </c>
       <c r="B8" t="n">
         <v>110061</v>
@@ -1389,26 +1398,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691318</v>
+        <v>691326</v>
       </c>
       <c r="R8" t="n">
-        <v>6684689</v>
+        <v>6684670</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119931411</v>
+        <v>119931614</v>
       </c>
       <c r="B9" t="n">
-        <v>97952</v>
+        <v>101097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R9" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119932296</v>
+        <v>119931706</v>
       </c>
       <c r="B3" t="n">
-        <v>97908</v>
+        <v>110061</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,46 +812,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691346</v>
+        <v>691300</v>
       </c>
       <c r="R3" t="n">
-        <v>6684612</v>
+        <v>6684669</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931454</v>
+        <v>119931537</v>
       </c>
       <c r="B4" t="n">
-        <v>97908</v>
+        <v>97952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R4" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -992,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119931706</v>
+        <v>119931411</v>
       </c>
       <c r="B5" t="n">
-        <v>110061</v>
+        <v>97952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691300</v>
+        <v>691258</v>
       </c>
       <c r="R5" t="n">
-        <v>6684669</v>
+        <v>6684672</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119931537</v>
+        <v>119931454</v>
       </c>
       <c r="B6" t="n">
-        <v>97952</v>
+        <v>97908</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R6" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119931411</v>
+        <v>119932296</v>
       </c>
       <c r="B7" t="n">
-        <v>97952</v>
+        <v>97908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,37 +1260,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691258</v>
+        <v>691346</v>
       </c>
       <c r="R7" t="n">
-        <v>6684672</v>
+        <v>6684612</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119931706</v>
+        <v>119932421</v>
       </c>
       <c r="B3" t="n">
         <v>110061</v>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691300</v>
+        <v>691326</v>
       </c>
       <c r="R3" t="n">
-        <v>6684669</v>
+        <v>6684670</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119931537</v>
+        <v>119931706</v>
       </c>
       <c r="B4" t="n">
-        <v>97952</v>
+        <v>110061</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219862</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691229</v>
+        <v>691300</v>
       </c>
       <c r="R4" t="n">
-        <v>6684627</v>
+        <v>6684669</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119931411</v>
+        <v>119932296</v>
       </c>
       <c r="B5" t="n">
-        <v>97952</v>
+        <v>97908</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,37 +1036,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691258</v>
+        <v>691346</v>
       </c>
       <c r="R5" t="n">
-        <v>6684672</v>
+        <v>6684612</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1244,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119932296</v>
+        <v>119931614</v>
       </c>
       <c r="B7" t="n">
-        <v>97908</v>
+        <v>101097</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,46 +1269,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691346</v>
+        <v>691229</v>
       </c>
       <c r="R7" t="n">
-        <v>6684612</v>
+        <v>6684627</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119932421</v>
+        <v>119931537</v>
       </c>
       <c r="B8" t="n">
-        <v>110061</v>
+        <v>97952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691326</v>
+        <v>691229</v>
       </c>
       <c r="R8" t="n">
-        <v>6684670</v>
+        <v>6684627</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119931614</v>
+        <v>119931411</v>
       </c>
       <c r="B9" t="n">
-        <v>101097</v>
+        <v>97952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691229</v>
+        <v>691258</v>
       </c>
       <c r="R9" t="n">
-        <v>6684627</v>
+        <v>6684672</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119932536</v>
+        <v>119931454</v>
       </c>
       <c r="B2" t="n">
-        <v>110061</v>
+        <v>97908</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>219798</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691318</v>
+        <v>691258</v>
       </c>
       <c r="R2" t="n">
-        <v>6684689</v>
+        <v>6684672</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119932421</v>
+        <v>119932536</v>
       </c>
       <c r="B3" t="n">
         <v>110061</v>
@@ -829,17 +820,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691326</v>
+        <v>691318</v>
       </c>
       <c r="R3" t="n">
-        <v>6684670</v>
+        <v>6684689</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119932296</v>
+        <v>119932421</v>
       </c>
       <c r="B5" t="n">
-        <v>97908</v>
+        <v>110061</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,46 +1036,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691346</v>
+        <v>691326</v>
       </c>
       <c r="R5" t="n">
-        <v>6684612</v>
+        <v>6684670</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1114,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119931454</v>
+        <v>119931411</v>
       </c>
       <c r="B6" t="n">
-        <v>97908</v>
+        <v>97952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1216,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119931614</v>
+        <v>119931537</v>
       </c>
       <c r="B7" t="n">
-        <v>101097</v>
+        <v>97952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221235</v>
+        <v>219862</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1365,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119931537</v>
+        <v>119932296</v>
       </c>
       <c r="B8" t="n">
-        <v>97952</v>
+        <v>97908</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,37 +1372,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691229</v>
+        <v>691346</v>
       </c>
       <c r="R8" t="n">
-        <v>6684627</v>
+        <v>6684612</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119931411</v>
+        <v>119931614</v>
       </c>
       <c r="B9" t="n">
-        <v>97952</v>
+        <v>101097</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R9" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 26279-2024 artfynd.xlsx
+++ b/artfynd/A 26279-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119931454</v>
+        <v>119931614</v>
       </c>
       <c r="B2" t="n">
-        <v>97908</v>
+        <v>101097</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R2" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119932421</v>
+        <v>119931411</v>
       </c>
       <c r="B5" t="n">
-        <v>110061</v>
+        <v>97952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,21 +1036,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219711</v>
+        <v>219862</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691326</v>
+        <v>691258</v>
       </c>
       <c r="R5" t="n">
-        <v>6684670</v>
+        <v>6684672</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1132,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119931411</v>
+        <v>119931537</v>
       </c>
       <c r="B6" t="n">
         <v>97952</v>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691258</v>
+        <v>691229</v>
       </c>
       <c r="R6" t="n">
-        <v>6684672</v>
+        <v>6684627</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119931537</v>
+        <v>119932296</v>
       </c>
       <c r="B7" t="n">
-        <v>97952</v>
+        <v>97908</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,37 +1260,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691229</v>
+        <v>691346</v>
       </c>
       <c r="R7" t="n">
-        <v>6684627</v>
+        <v>6684612</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1365,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119932296</v>
+        <v>119931454</v>
       </c>
       <c r="B8" t="n">
         <v>97908</v>
@@ -1389,29 +1398,20 @@
           <t>(L.) Crantz</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Örsberg, Örsberg, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691346</v>
+        <v>691258</v>
       </c>
       <c r="R8" t="n">
-        <v>6684612</v>
+        <v>6684672</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119931614</v>
+        <v>119932421</v>
       </c>
       <c r="B9" t="n">
-        <v>101097</v>
+        <v>110061</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>219711</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691229</v>
+        <v>691326</v>
       </c>
       <c r="R9" t="n">
-        <v>6684627</v>
+        <v>6684670</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
